--- a/Data/01_VehicleElectronics.xlsx
+++ b/Data/01_VehicleElectronics.xlsx
@@ -35,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,6 +87,13 @@
       <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="10">
@@ -196,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -240,6 +247,11 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1711,17 +1723,17 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="I10" s="7" t="n">
@@ -1823,17 +1835,17 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="I11" s="7" t="n">
@@ -1940,12 +1952,12 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="I12" s="7" t="n">
@@ -14773,17 +14785,17 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="I2" s="13" t="n">
@@ -14890,12 +14902,12 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="I3" s="13" t="n">
@@ -14997,7 +15009,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -15007,7 +15019,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="I4" s="13" t="n">

--- a/Data/01_VehicleElectronics.xlsx
+++ b/Data/01_VehicleElectronics.xlsx
@@ -1387,17 +1387,17 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="I7" s="7" t="n">
@@ -1499,17 +1499,17 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
           <t>Opt</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Std</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Std</t>
         </is>
       </c>
       <c r="I8" s="7" t="n">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Opt</t>
         </is>
       </c>
       <c r="I9" s="7" t="n">

--- a/Data/01_VehicleElectronics.xlsx
+++ b/Data/01_VehicleElectronics.xlsx
@@ -11576,7 +11576,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I6" s="13" t="n">
@@ -14382,7 +14382,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Opt</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I12" s="7" t="n">
